--- a/Excel/BootstrapLocale.xlsx
+++ b/Excel/BootstrapLocale.xlsx
@@ -6,7 +6,6 @@
     <sheet state="visible" name="Ko" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Jp" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="En" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="Enum_LanguageType" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -14,12 +13,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="60">
   <si>
     <t>&lt;DataName&gt;LocaleEntry&lt;/DataName&gt;</t>
   </si>
   <si>
     <t>&lt;Language&gt;Ko&lt;/Language&gt;</t>
+  </si>
+  <si>
+    <t>&lt;SharesRowType&gt;true&lt;/SharesRowType&gt;</t>
+  </si>
+  <si>
+    <t>&lt;SharesRootType&gt;true&lt;/SharesRootType&gt;</t>
   </si>
   <si>
     <t>Id:int</t>
@@ -189,24 +194,6 @@
   <si>
     <t>Server maintenance is currently in progress.</t>
   </si>
-  <si>
-    <t>&lt;EnumType=Normal&gt;</t>
-  </si>
-  <si>
-    <t>EnumName</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Ko</t>
-  </si>
-  <si>
-    <t>Jp</t>
-  </si>
-  <si>
-    <t>En</t>
-  </si>
 </sst>
 </file>
 
@@ -265,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -274,6 +261,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
@@ -287,9 +277,6 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -299,15 +286,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -326,10 +304,6 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -564,182 +538,180 @@
       <c r="E2" s="2"/>
     </row>
     <row r="3">
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="5">
+      <c r="D5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="6">
         <v>1.0</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="5">
+      <c r="D6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="6">
         <v>2.0</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6">
-      <c r="B6" s="5">
+      <c r="D7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="6">
         <v>3.0</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="5">
+      <c r="D8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="6">
         <v>4.0</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="5">
+      <c r="D9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="6">
         <v>5.0</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="5">
+      <c r="D10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="6">
         <v>6.0</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="5">
+      <c r="D11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="6">
         <v>7.0</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="5">
+      <c r="D12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="6">
         <v>8.0</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="5">
+      <c r="D13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="6">
         <v>9.0</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="7"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="5">
+      <c r="D14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="6">
         <v>10.0</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="2"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="2"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="D15" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="3"/>
     </row>
     <row r="16">
       <c r="B16" s="2"/>
@@ -5695,7 +5667,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5703,50 +5675,36 @@
       <c r="E2" s="2"/>
     </row>
     <row r="3">
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="4" t="s">
+    </row>
+    <row r="5">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="8">
-        <f t="array" ref="B4:C1000">Ko!B4:C1000</f>
+      <c r="D5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="8">
+        <f t="array" ref="B6:C1000">Ko!B6:C1000</f>
         <v>1</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="9"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="9"/>
-    </row>
-    <row r="6">
-      <c r="B6" s="8">
-        <v>3.0</v>
-      </c>
       <c r="C6" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>39</v>
@@ -5755,10 +5713,10 @@
     </row>
     <row r="7">
       <c r="B7" s="8">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>40</v>
@@ -5767,10 +5725,10 @@
     </row>
     <row r="8">
       <c r="B8" s="8">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>41</v>
@@ -5779,10 +5737,10 @@
     </row>
     <row r="9">
       <c r="B9" s="8">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>42</v>
@@ -5791,10 +5749,10 @@
     </row>
     <row r="10">
       <c r="B10" s="8">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>43</v>
@@ -5803,10 +5761,10 @@
     </row>
     <row r="11">
       <c r="B11" s="8">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>44</v>
@@ -5815,10 +5773,10 @@
     </row>
     <row r="12">
       <c r="B12" s="8">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>45</v>
@@ -5827,10 +5785,10 @@
     </row>
     <row r="13">
       <c r="B13" s="8">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>46</v>
@@ -5838,12 +5796,28 @@
       <c r="E13" s="9"/>
     </row>
     <row r="14">
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
+      <c r="B14" s="8">
+        <v>9.0</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="9"/>
     </row>
     <row r="15">
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
+      <c r="B15" s="8">
+        <v>10.0</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="9"/>
     </row>
     <row r="16">
       <c r="B16" s="8"/>
@@ -9821,7 +9795,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="30.13"/>
+    <col customWidth="1" min="1" max="1" width="40.25"/>
     <col customWidth="1" min="3" max="3" width="26.13"/>
     <col customWidth="1" min="4" max="4" width="37.63"/>
     <col customWidth="1" min="5" max="5" width="27.75"/>
@@ -9838,7 +9812,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -9846,48 +9820,36 @@
       <c r="E2" s="2"/>
     </row>
     <row r="3">
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="4" t="s">
+    </row>
+    <row r="5">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="8">
-        <f t="array" ref="B4:C1000">Ko!B4:C1000</f>
+      <c r="D5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="8">
+        <f t="array" ref="B6:C1000">Ko!B6:C1000</f>
         <v>1</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="8">
-        <v>3.0</v>
-      </c>
       <c r="C6" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>50</v>
@@ -9895,10 +9857,10 @@
     </row>
     <row r="7">
       <c r="B7" s="8">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>51</v>
@@ -9906,10 +9868,10 @@
     </row>
     <row r="8">
       <c r="B8" s="8">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>52</v>
@@ -9917,10 +9879,10 @@
     </row>
     <row r="9">
       <c r="B9" s="8">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>53</v>
@@ -9928,10 +9890,10 @@
     </row>
     <row r="10">
       <c r="B10" s="8">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>54</v>
@@ -9939,10 +9901,10 @@
     </row>
     <row r="11">
       <c r="B11" s="8">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>55</v>
@@ -9950,10 +9912,10 @@
     </row>
     <row r="12">
       <c r="B12" s="8">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>56</v>
@@ -9961,22 +9923,36 @@
     </row>
     <row r="13">
       <c r="B13" s="8">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
+      <c r="B14" s="8">
+        <v>9.0</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
+      <c r="B15" s="8">
+        <v>10.0</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="8"/>
@@ -13955,56 +13931,4 @@
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="17.25"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="12"/>
-      <c r="B2" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12"/>
-      <c r="B3" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" s="14">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" s="1">
-        <v>2.0</v>
-      </c>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>